--- a/assets/constructions/examples/ctd_collet_tapping.xlsx
+++ b/assets/constructions/examples/ctd_collet_tapping.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ctd" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="ctd" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V6"/>
+  <dimension ref="A1:Z6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -539,11 +539,31 @@
           <t>releasepack</t>
         </is>
       </c>
+      <c r="W1" s="1" t="inlineStr">
+        <is>
+          <t>lcs</t>
+        </is>
+      </c>
+      <c r="X1" s="1" t="inlineStr">
+        <is>
+          <t>pricevalue</t>
+        </is>
+      </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>pricecurrency</t>
+        </is>
+      </c>
+      <c r="Z1" s="1" t="inlineStr">
+        <is>
+          <t>pricevalue_rub</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>G022V-40x20</t>
+          <t>G022V-40x11</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -565,12 +585,12 @@
         <v>41</v>
       </c>
       <c r="H2" t="n">
-        <v>20</v>
+        <v>11</v>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="J2" t="inlineStr">
         <is>
-          <t>DCON_X_DRVS:20X16</t>
+          <t>DCON_X_DRVS:11x9</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -584,7 +604,7 @@
         <v>0</v>
       </c>
       <c r="O2" t="n">
-        <v>16</v>
+        <v>9</v>
       </c>
       <c r="P2" t="inlineStr"/>
       <c r="Q2" t="n">
@@ -609,11 +629,17 @@
           <t>https://www.kfh-hermann.de/</t>
         </is>
       </c>
+      <c r="W2" t="n">
+        <v>1</v>
+      </c>
+      <c r="X2" t="inlineStr"/>
+      <c r="Y2" t="inlineStr"/>
+      <c r="Z2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>G022V-32x18</t>
+          <t>G022V-32x9</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -635,12 +661,12 @@
         <v>33</v>
       </c>
       <c r="H3" t="n">
-        <v>18</v>
+        <v>9</v>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="J3" t="inlineStr">
         <is>
-          <t>DCON_X_DRVS:18X14.5</t>
+          <t>DCON_X_DRVS:9x7</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -654,7 +680,7 @@
         <v>0</v>
       </c>
       <c r="O3" t="n">
-        <v>14.5</v>
+        <v>7</v>
       </c>
       <c r="P3" t="inlineStr"/>
       <c r="Q3" t="n">
@@ -679,11 +705,17 @@
           <t>https://www.kfh-hermann.de/</t>
         </is>
       </c>
+      <c r="W3" t="n">
+        <v>1</v>
+      </c>
+      <c r="X3" t="inlineStr"/>
+      <c r="Y3" t="inlineStr"/>
+      <c r="Z3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>G022V-32x3.5</t>
+          <t>G022V-40x10</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -697,20 +729,20 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>40</v>
+        <v>46</v>
       </c>
       <c r="E4" t="inlineStr"/>
       <c r="F4" t="inlineStr"/>
       <c r="G4" t="n">
-        <v>33</v>
+        <v>41</v>
       </c>
       <c r="H4" t="n">
-        <v>3.5</v>
+        <v>10</v>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="J4" t="inlineStr">
         <is>
-          <t>DCON_X_DRVS:3.5X2.7</t>
+          <t>DCON_X_DRVS:10x8</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -724,7 +756,7 @@
         <v>0</v>
       </c>
       <c r="O4" t="n">
-        <v>2.7</v>
+        <v>8</v>
       </c>
       <c r="P4" t="inlineStr"/>
       <c r="Q4" t="n">
@@ -732,7 +764,7 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>ER32</t>
+          <t>ER40</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
@@ -749,11 +781,17 @@
           <t>https://www.kfh-hermann.de/</t>
         </is>
       </c>
+      <c r="W4" t="n">
+        <v>1</v>
+      </c>
+      <c r="X4" t="inlineStr"/>
+      <c r="Y4" t="inlineStr"/>
+      <c r="Z4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>G022V-32x4.5</t>
+          <t>G022V-40x9</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -767,20 +805,20 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>40</v>
+        <v>46</v>
       </c>
       <c r="E5" t="inlineStr"/>
       <c r="F5" t="inlineStr"/>
       <c r="G5" t="n">
-        <v>33</v>
+        <v>41</v>
       </c>
       <c r="H5" t="n">
-        <v>4.5</v>
+        <v>9</v>
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="J5" t="inlineStr">
         <is>
-          <t>DCON_X_DRVS:4.5X3.4</t>
+          <t>DCON_X_DRVS:9x7</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -794,7 +832,7 @@
         <v>0</v>
       </c>
       <c r="O5" t="n">
-        <v>3.4</v>
+        <v>7</v>
       </c>
       <c r="P5" t="inlineStr"/>
       <c r="Q5" t="n">
@@ -802,7 +840,7 @@
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>ER32</t>
+          <t>ER40</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
@@ -819,11 +857,17 @@
           <t>https://www.kfh-hermann.de/</t>
         </is>
       </c>
+      <c r="W5" t="n">
+        <v>1</v>
+      </c>
+      <c r="X5" t="inlineStr"/>
+      <c r="Y5" t="inlineStr"/>
+      <c r="Z5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>G022V-40x9</t>
+          <t>G022V-32x6</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -837,20 +881,20 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>46</v>
+        <v>40</v>
       </c>
       <c r="E6" t="inlineStr"/>
       <c r="F6" t="inlineStr"/>
       <c r="G6" t="n">
-        <v>41</v>
+        <v>33</v>
       </c>
       <c r="H6" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="I6" t="inlineStr"/>
       <c r="J6" t="inlineStr">
         <is>
-          <t>DCON_X_DRVS:9X7</t>
+          <t>DCON_X_DRVS:6x4.9</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -864,7 +908,7 @@
         <v>0</v>
       </c>
       <c r="O6" t="n">
-        <v>7</v>
+        <v>4.9</v>
       </c>
       <c r="P6" t="inlineStr"/>
       <c r="Q6" t="n">
@@ -872,7 +916,7 @@
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>ER40</t>
+          <t>ER32</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
@@ -889,6 +933,12 @@
           <t>https://www.kfh-hermann.de/</t>
         </is>
       </c>
+      <c r="W6" t="n">
+        <v>1</v>
+      </c>
+      <c r="X6" t="inlineStr"/>
+      <c r="Y6" t="inlineStr"/>
+      <c r="Z6" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
